--- a/invoices/invoice_2026-06-29.xlsx
+++ b/invoices/invoice_2026-06-29.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PAID</t>
         </is>
       </c>
     </row>
@@ -694,14 +694,14 @@
     <row r="16" ht="28" customHeight="1">
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Data Analysis &amp; Reporting</t>
+          <t>Cloud Infrastructure Setup</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>600000</v>
+        <v>1200000</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>0.11</v>
@@ -714,14 +714,14 @@
     <row r="17" ht="28" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>UI/UX Design Services</t>
+          <t>Software Development</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>750000</v>
+        <v>5000000</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>0.11</v>
